--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_129_R13.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_129_R13.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8473</v>
+        <v>8.1744</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2029</v>
+        <v>8.3956</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3556</v>
+        <v>-0.2212</v>
       </c>
       <c r="G2" t="n">
         <v>2.1337</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>0.644</v>
+        <v>0.9711</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1483</v>
+        <v>1.341</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5043</v>
+        <v>-0.3699</v>
       </c>
       <c r="V2" t="n">
         <v>2.2862</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1384</v>
+        <v>4.956</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6514</v>
+        <v>1.2674</v>
       </c>
       <c r="F3" t="n">
-        <v>3.487</v>
+        <v>3.6886</v>
       </c>
       <c r="G3" t="n">
         <v>1.2169</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9732</v>
+        <v>1.7908</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9371</v>
+        <v>1.5531</v>
       </c>
       <c r="U3" t="n">
-        <v>0.036</v>
+        <v>0.2377</v>
       </c>
       <c r="V3" t="n">
         <v>0.7886</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4232</v>
+        <v>4.0706</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5813</v>
+        <v>2.1278</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8419</v>
+        <v>1.9427</v>
       </c>
       <c r="G4" t="n">
         <v>4.1963</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6286</v>
+        <v>0.0187</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4402</v>
+        <v>0.1063</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1885</v>
+        <v>-0.0876</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0722</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1829</v>
+        <v>3.0661</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3998</v>
+        <v>1.1822</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7831</v>
+        <v>1.8839</v>
       </c>
       <c r="G5" t="n">
         <v>0.7911</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1419</v>
+        <v>1.0251</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0158</v>
+        <v>0.7982</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1261</v>
+        <v>0.2269</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1418</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5839</v>
+        <v>2.0626</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3112</v>
+        <v>0.6218</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2728</v>
+        <v>1.4408</v>
       </c>
       <c r="G6" t="n">
         <v>0.8996</v>
@@ -922,13 +922,13 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6664</v>
+        <v>1.145</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.8887</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0883</v>
+        <v>0.2563</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6778999999999999</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4999</v>
+        <v>0.5815</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4605</v>
+        <v>1.9455</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9607</v>
+        <v>-1.3639</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2076</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4987</v>
+        <v>1.5804</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5885</v>
+        <v>1.0734</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9102</v>
+        <v>0.507</v>
       </c>
       <c r="V7" t="n">
         <v>-1.719</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0329</v>
+        <v>0.1022</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0453</v>
+        <v>0.1906</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0124</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2644</v>
@@ -1078,13 +1078,13 @@
         <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0004</v>
+        <v>0.1346</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1494</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1489</v>
+        <v>0.0481</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0563</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7623</v>
+        <v>-1.7987</v>
       </c>
       <c r="F9" t="n">
-        <v>0.706</v>
+        <v>0.9152</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0649</v>
+        <v>-1.8088</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.6606</v>
+        <v>-1.3336</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5957</v>
+        <v>-0.4752</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1538</v>
+        <v>-1.1936</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.2274</v>
+        <v>-0.5644</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0736</v>
+        <v>-0.6292</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08890000000000001</v>
+        <v>-0.6152</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4331</v>
+        <v>-0.7692</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5221</v>
+        <v>0.154</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7834</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3977</v>
+        <v>-0.0953</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3501</v>
+        <v>0.5546</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9524</v>
+        <v>-0.6499</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4665</v>
+        <v>0.7886</v>
       </c>
       <c r="W9" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.214</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9115</v>
+        <v>-1.2656</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8603</v>
+        <v>-1.32</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9488</v>
+        <v>0.0543</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8088</v>
+        <v>-1.3333</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3336</v>
+        <v>-1.0923</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4752</v>
+        <v>-0.2409</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1936</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5644</v>
+        <v>-0.3123</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6292</v>
+        <v>-0.3949</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6152</v>
+        <v>-0.626</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7692</v>
+        <v>-0.78</v>
       </c>
       <c r="O10" t="n">
         <v>0.154</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1233</v>
+        <v>-0.002</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.507</v>
+        <v>0.4052</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6163</v>
+        <v>-0.4072</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7886</v>
+        <v>-0.3943</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7886</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0658</v>
+        <v>-1.8524</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4562</v>
+        <v>-2.6928</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3904</v>
+        <v>0.8404</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3333</v>
+        <v>-2.0649</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0923</v>
+        <v>-2.6606</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2409</v>
+        <v>0.5957</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-2.1538</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3123</v>
+        <v>-2.2274</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3949</v>
+        <v>0.0736</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.626</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.78</v>
+        <v>-0.4331</v>
       </c>
       <c r="O11" t="n">
-        <v>0.154</v>
+        <v>0.5221</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>2.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8022</v>
+        <v>0.6016</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.731</v>
+        <v>1.4196</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0712</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3943</v>
+        <v>1.4665</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1418</v>
+        <v>2.6805</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5361</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3579</v>
+        <v>-2.216</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2463</v>
+        <v>-1.1716</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1116</v>
+        <v>-1.0444</v>
       </c>
       <c r="G12" t="n">
         <v>0.4297</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4112</v>
+        <v>-0.2693</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3541</v>
+        <v>0.4288</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7653</v>
+        <v>-0.698</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1444</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8786</v>
+        <v>-2.6763</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7674</v>
+        <v>-1.5315</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1112</v>
+        <v>-1.1448</v>
       </c>
       <c r="G13" t="n">
         <v>-1.3972</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.105</v>
+        <v>0.0973</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1937</v>
+        <v>0.1601</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6083</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.3726</v>
+        <v>14.1195</v>
       </c>
       <c r="E14" t="n">
-        <v>6.4693</v>
+        <v>7.216300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>6.9033</v>
+        <v>6.903200000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>2.591100000000001</v>
+        <v>2.591100000000002</v>
       </c>
       <c r="H14" t="n">
         <v>-2.9299</v>
@@ -1528,7 +1528,7 @@
         <v>1.873</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5757</v>
+        <v>-0.5757000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-4.2233</v>
@@ -1537,7 +1537,7 @@
         <v>3.648</v>
       </c>
       <c r="P14" t="n">
-        <v>6.958699999999999</v>
+        <v>6.958700000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-12.7575</v>
@@ -1546,13 +1546,13 @@
         <v>19.716</v>
       </c>
       <c r="S14" t="n">
-        <v>6.251199999999999</v>
+        <v>6.997999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>7.845700000000001</v>
+        <v>8.592600000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5948</v>
+        <v>-1.5945</v>
       </c>
       <c r="V14" t="n">
         <v>-2.428000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8639</v>
+        <v>7.3801</v>
       </c>
       <c r="E15" t="n">
-        <v>6.3913</v>
+        <v>7.3349</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5274</v>
+        <v>0.0453</v>
       </c>
       <c r="G15" t="n">
         <v>6.1835</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9694</v>
+        <v>-0.4531</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0455</v>
+        <v>-0.1019</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9238</v>
+        <v>-0.3512</v>
       </c>
       <c r="V15" t="n">
         <v>5.361</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5265</v>
+        <v>1.5259</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4951</v>
+        <v>0.2126</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0216</v>
+        <v>1.3133</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6274</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.078</v>
+        <v>-0.0786</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3576</v>
+        <v>0.3501</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7204</v>
+        <v>-0.4288</v>
       </c>
       <c r="V16" t="n">
         <v>1.0722</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7287</v>
+        <v>-0.5392</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9916</v>
+        <v>-0.3543</v>
       </c>
       <c r="F17" t="n">
-        <v>0.263</v>
+        <v>-0.1849</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8149</v>
+        <v>0.9323</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3939</v>
+        <v>2.1403</v>
       </c>
       <c r="I17" t="n">
-        <v>0.579</v>
+        <v>-1.2079</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2923</v>
+        <v>0.7464</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4027</v>
+        <v>1.5327</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1104</v>
+        <v>-0.7863</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5226</v>
+        <v>0.186</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9912</v>
+        <v>0.6075</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4685</v>
+        <v>-0.4216</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6223</v>
+        <v>-0.402</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6201</v>
+        <v>0.0591</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0022</v>
+        <v>-0.461</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9152</v>
+        <v>-1.0604</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4722</v>
+        <v>-0.1318</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.443</v>
+        <v>-0.9286</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9323</v>
+        <v>-1.3531</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1403</v>
+        <v>-1.0888</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2079</v>
+        <v>-0.2643</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7464</v>
+        <v>-1.5391</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5327</v>
+        <v>-1.5391</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0.186</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6075</v>
+        <v>0.4502</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4216</v>
+        <v>-0.2643</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.778</v>
+        <v>-0.3646</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0589</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7191</v>
+        <v>-0.2743</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1418</v>
+        <v>0.4254</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.4975</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>M. NDIAYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1004</v>
+        <v>-1.3685</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2498</v>
+        <v>-1.2093</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8507</v>
+        <v>-0.1592</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3531</v>
+        <v>-0.145</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0888</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2643</v>
+        <v>-1.1041</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5391</v>
+        <v>-0.4131</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5391</v>
+        <v>0.3732</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.7863</v>
       </c>
       <c r="M19" t="n">
-        <v>0.186</v>
+        <v>0.2681</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4502</v>
+        <v>0.586</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2643</v>
+        <v>-0.3178</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4046</v>
+        <v>-0.6152</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2082</v>
+        <v>-0.3143</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1964</v>
+        <v>-0.3009</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4254</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4975</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. NDIAYE</t>
+          <t>M. NGOUAMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2392</v>
+        <v>-1.4563</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8555</v>
+        <v>-0.9357</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3837</v>
+        <v>-0.5206</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.145</v>
+        <v>-0.8506</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9592000000000001</v>
+        <v>-0.0108</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1041</v>
+        <v>-0.8399</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4131</v>
+        <v>-0.7863</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3732</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>-0.7863</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2681</v>
+        <v>-0.0643</v>
       </c>
       <c r="N20" t="n">
-        <v>0.586</v>
+        <v>-0.0108</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3178</v>
+        <v>-0.0535</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4859</v>
+        <v>-0.4639</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0395</v>
+        <v>-0.1494</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5254</v>
+        <v>-0.3145</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7501</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. NGOUAMA</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6136</v>
+        <v>-1.9569</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9357</v>
+        <v>-2.0532</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.0963</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8506</v>
+        <v>-0.8149</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0108</v>
+        <v>-1.3939</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8399</v>
+        <v>0.579</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7863</v>
+        <v>-0.2923</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.4027</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7863</v>
+        <v>0.1104</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0643</v>
+        <v>-0.5226</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0108</v>
+        <v>-0.9912</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0535</v>
+        <v>0.4685</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6212</v>
+        <v>0.3941</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1494</v>
+        <v>0.5586</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4718</v>
+        <v>-0.1645</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2769</v>
+        <v>-2.0588</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4489</v>
+        <v>-0.1409</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7258</v>
+        <v>-1.918</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8623</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9867</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6844</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.6711</v>
+        <v>-0.8632</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8197</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2966</v>
+        <v>-3.1228</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0696</v>
+        <v>-3.1876</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2269</v>
+        <v>0.0648</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3169</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2838</v>
+        <v>-0.11</v>
       </c>
       <c r="T23" t="n">
-        <v>0.362</v>
+        <v>0.244</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6458</v>
+        <v>-0.3541</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.152</v>
+        <v>-3.1577</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9749</v>
+        <v>-1.3851</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1772</v>
+        <v>-1.7726</v>
       </c>
       <c r="G24" t="n">
         <v>-0.06270000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3935</v>
+        <v>-0.3991</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1256</v>
+        <v>0.4641</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2678</v>
+        <v>-0.8632</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4405</v>
+        <v>-4.4126</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.163</v>
+        <v>-4.5168</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2776</v>
+        <v>0.1042</v>
       </c>
       <c r="G25" t="n">
         <v>-1.6738</v>
@@ -2404,13 +2404,13 @@
         <v>1.8556</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1274</v>
+        <v>0.1553</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8338</v>
+        <v>0.4799</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7064</v>
+        <v>-0.3246</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1107</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.3727</v>
+        <v>-10.2272</v>
       </c>
       <c r="E26" t="n">
         <v>-6.3672</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.005599999999998</v>
+        <v>-3.86</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.5909</v>
+        <v>-2.590899999999999</v>
       </c>
       <c r="H26" t="n">
         <v>2.9299</v>
@@ -2455,10 +2455,10 @@
         <v>-5.520699999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5756999999999991</v>
+        <v>0.5757</v>
       </c>
       <c r="K26" t="n">
-        <v>4.2234</v>
+        <v>4.223400000000001</v>
       </c>
       <c r="L26" t="n">
         <v>-3.647699999999999</v>
@@ -2482,13 +2482,13 @@
         <v>12.7576</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.2514</v>
+        <v>-3.1057</v>
       </c>
       <c r="T26" t="n">
         <v>1.5946</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.845800000000001</v>
+        <v>-4.7003</v>
       </c>
       <c r="V26" t="n">
         <v>2.427999999999999</v>
